--- a/data/trans_orig/IP16B08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B08-Estudios-trans_orig.xlsx
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>28227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>49,22%</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
